--- a/Uligarm_imports.xlsx
+++ b/Uligarm_imports.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elias\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\UligarmPage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E3A6C10-43C9-4B04-91D2-DE082F184CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8FCAA0-0020-43B1-8449-878110B87793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D9E622A8-95F9-42AD-B0D8-E844E2101417}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
   <si>
     <t>player_name</t>
   </si>
@@ -182,9 +182,6 @@
     <t>Hechicero</t>
   </si>
   <si>
-    <t>CarlaP</t>
-  </si>
-  <si>
     <t>RaquelA</t>
   </si>
   <si>
@@ -236,14 +233,56 @@
     <t>Sombras</t>
   </si>
   <si>
-    <t xml:space="preserve">El usuario puede viajar mediante las sombras, recibiendo 1D4 de daño mediante un chance, calculado como "1/2^(8-n)", siendo n el numero de veces que se usa la habilidad antes de un descanso largo. </t>
+    <t>Ibro Hamok</t>
+  </si>
+  <si>
+    <t>Swap</t>
+  </si>
+  <si>
+    <t>Realiza un cambio de almas entre el usuario y su contratante que dura 1 minuto (fuera de combate) o 2 turnos (dentro de combate). El alma del usuario vuelve una vez pasado el tiempo, todo el daño recibido es compartido. Si el contratante es derrotado antes de que se acabe el tiempo, el usuario vuelve sin rasjuños.</t>
+  </si>
+  <si>
+    <t>Raychin Gueña</t>
+  </si>
+  <si>
+    <t>Suena el Punch</t>
+  </si>
+  <si>
+    <t>El usuario acumula todo el daño inflingido, recibido y curado en el turno, para liberarlo en un golpe devastador en su siguiente ataque. Este golpe equivale a 1D12 + acumulado. En caso que no pueda acumular nada, el objetivo obtendra un estado negativo elegido por el usuario: Stun (20 segundos / 1 turno), Sangrado (30 segundos / 2 turnos) o Confusion (40 segundos / 3 Turnos)</t>
+  </si>
+  <si>
+    <t>Humano+</t>
+  </si>
+  <si>
+    <t>Lucanar Tarknus</t>
+  </si>
+  <si>
+    <t>Iron Maiden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario puede viajar mediante las sombras (hasta 25 metros de distancia), recibiendo 1D4 de daño mediante un chance, calculado como "1/2^(8-n)", siendo n el numero de veces que se usa la habilidad antes de un descanso largo. </t>
+  </si>
+  <si>
+    <t>El usuario es capaz de manipular los metales que lo rodean (hasta 25 metros de distancia), haciendo formas varias de defensas y ataques que benefician a si mismo y a sus aliados.</t>
+  </si>
+  <si>
+    <t>Krivna Jeryn</t>
+  </si>
+  <si>
+    <t>Sora</t>
+  </si>
+  <si>
+    <t>CarlaB</t>
+  </si>
+  <si>
+    <t>Aguila. Stats: 8STR ; 18DEX ; 10CON ; 10INT ; 12WIS ; 14CAR. Puede causar un destello cegante a merced de su usuario (20 segundos / 1 turno), ademas, puede volar por su cuenta (30 metros de altura, alejarse 20 metros del usuario maximo en otra direccion) y el usuario puede ver a traves de los ojos de Sora, quedando limitado a ver lo que este hace (no puede hacer mas que ver a traves de Sora y hablar con su propio cuerpo).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,7 +314,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -292,10 +331,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -616,36 +651,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC77910-4458-41B4-971B-CA59A354520A}">
   <dimension ref="A1:X13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="49.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="49.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="22" max="22" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -719,7 +754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="85.5">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -729,6 +764,9 @@
       <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
@@ -746,6 +784,12 @@
       </c>
       <c r="J2" s="1">
         <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="M2" s="1">
         <v>5</v>
@@ -790,7 +834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="114">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -800,6 +844,9 @@
       <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
@@ -817,6 +864,12 @@
       </c>
       <c r="J3" s="1">
         <v>1</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="M3" s="1">
         <v>14</v>
@@ -861,7 +914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="71.25">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
@@ -941,7 +994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24">
       <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
@@ -1012,7 +1065,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="57">
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
@@ -1022,6 +1075,9 @@
       <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
@@ -1032,13 +1088,19 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>44</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="M6" s="1">
         <v>11</v>
@@ -1083,7 +1145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="114">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
@@ -1093,6 +1155,9 @@
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
       </c>
@@ -1106,10 +1171,16 @@
         <v>43</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="M7" s="1">
         <v>9</v>
@@ -1154,9 +1225,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
@@ -1177,7 +1248,7 @@
         <v>43</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
@@ -1225,9 +1296,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1">
         <v>8</v>
@@ -1245,19 +1316,19 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="M9" s="1">
         <v>10</v>
@@ -1302,18 +1373,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>26</v>
@@ -1328,16 +1399,16 @@
         <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J10" s="1">
         <v>2</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="M10" s="1">
         <v>9</v>
@@ -1382,15 +1453,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24">
       <c r="A11" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>39</v>
@@ -1402,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
@@ -1453,15 +1524,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>39</v>
@@ -1473,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>47</v>
@@ -1524,18 +1595,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="57">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1544,14 +1615,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7c5d65ae-dd4c-42e9-a760-1483bb566e2c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006FE3DCCD7373024E84EE2E195A0A7460" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="9c5fe5080737f498835bd2d9d4e78e12">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7c5d65ae-dd4c-42e9-a760-1483bb566e2c" xmlns:ns4="ecb6ce5d-d8b9-4a2b-93be-18f353c43254" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a74015842085a18a3a3b1f516f0630d7" ns3:_="" ns4:_="">
     <xsd:import namespace="7c5d65ae-dd4c-42e9-a760-1483bb566e2c"/>
@@ -1778,7 +1841,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1787,24 +1850,15 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19622B12-5B3A-4BF4-AEA6-C94284661AF9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ecb6ce5d-d8b9-4a2b-93be-18f353c43254"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="7c5d65ae-dd4c-42e9-a760-1483bb566e2c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7c5d65ae-dd4c-42e9-a760-1483bb566e2c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE75FF8-4343-4CB1-8F7E-27C6332DD2BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1823,10 +1877,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19622B12-5B3A-4BF4-AEA6-C94284661AF9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="ecb6ce5d-d8b9-4a2b-93be-18f353c43254"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="7c5d65ae-dd4c-42e9-a760-1483bb566e2c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Uligarm_imports.xlsx
+++ b/Uligarm_imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\UligarmPage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8FCAA0-0020-43B1-8449-878110B87793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3B0F33-335B-4AD0-B498-C858A7B06D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D9E622A8-95F9-42AD-B0D8-E844E2101417}"/>
   </bookViews>
@@ -1402,7 +1402,7 @@
         <v>56</v>
       </c>
       <c r="J10" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>57</v>
@@ -1601,6 +1601,9 @@
       </c>
       <c r="B13" s="1">
         <v>9</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>64</v>
@@ -1615,6 +1618,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006FE3DCCD7373024E84EE2E195A0A7460" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="9c5fe5080737f498835bd2d9d4e78e12">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7c5d65ae-dd4c-42e9-a760-1483bb566e2c" xmlns:ns4="ecb6ce5d-d8b9-4a2b-93be-18f353c43254" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a74015842085a18a3a3b1f516f0630d7" ns3:_="" ns4:_="">
     <xsd:import namespace="7c5d65ae-dd4c-42e9-a760-1483bb566e2c"/>
@@ -1841,15 +1853,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1859,6 +1862,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE75FF8-4343-4CB1-8F7E-27C6332DD2BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1873,14 +1884,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Uligarm_imports.xlsx
+++ b/Uligarm_imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\UligarmPage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3B0F33-335B-4AD0-B498-C858A7B06D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0F371F-A305-4A17-BCC8-610FC52D1359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D9E622A8-95F9-42AD-B0D8-E844E2101417}"/>
   </bookViews>
@@ -1618,15 +1618,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006FE3DCCD7373024E84EE2E195A0A7460" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="9c5fe5080737f498835bd2d9d4e78e12">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7c5d65ae-dd4c-42e9-a760-1483bb566e2c" xmlns:ns4="ecb6ce5d-d8b9-4a2b-93be-18f353c43254" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a74015842085a18a3a3b1f516f0630d7" ns3:_="" ns4:_="">
     <xsd:import namespace="7c5d65ae-dd4c-42e9-a760-1483bb566e2c"/>
@@ -1853,6 +1844,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1862,14 +1862,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE75FF8-4343-4CB1-8F7E-27C6332DD2BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1884,6 +1876,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Uligarm_imports.xlsx
+++ b/Uligarm_imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\UligarmPage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0F371F-A305-4A17-BCC8-610FC52D1359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087288C9-0852-492B-8BF3-9C7B2054F6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D9E622A8-95F9-42AD-B0D8-E844E2101417}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="81">
   <si>
     <t>player_name</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>Aguila. Stats: 8STR ; 18DEX ; 10CON ; 10INT ; 12WIS ; 14CAR. Puede causar un destello cegante a merced de su usuario (20 segundos / 1 turno), ademas, puede volar por su cuenta (30 metros de altura, alejarse 20 metros del usuario maximo en otra direccion) y el usuario puede ver a traves de los ojos de Sora, quedando limitado a ver lo que este hace (no puede hacer mas que ver a traves de Sora y hablar con su propio cuerpo).</t>
+  </si>
+  <si>
+    <t>Sira Strand</t>
   </si>
 </sst>
 </file>
@@ -1306,6 +1309,9 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
       </c>
@@ -1618,6 +1624,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006FE3DCCD7373024E84EE2E195A0A7460" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="9c5fe5080737f498835bd2d9d4e78e12">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7c5d65ae-dd4c-42e9-a760-1483bb566e2c" xmlns:ns4="ecb6ce5d-d8b9-4a2b-93be-18f353c43254" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a74015842085a18a3a3b1f516f0630d7" ns3:_="" ns4:_="">
     <xsd:import namespace="7c5d65ae-dd4c-42e9-a760-1483bb566e2c"/>
@@ -1844,15 +1859,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1862,6 +1868,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE75FF8-4343-4CB1-8F7E-27C6332DD2BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1876,14 +1890,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Uligarm_imports.xlsx
+++ b/Uligarm_imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\UligarmPage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087288C9-0852-492B-8BF3-9C7B2054F6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC4DCD8-170F-45B2-B6D2-21E2EE79F887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D9E622A8-95F9-42AD-B0D8-E844E2101417}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="87">
   <si>
     <t>player_name</t>
   </si>
@@ -194,9 +194,6 @@
     <t>Princesita</t>
   </si>
   <si>
-    <t>OsoBuho. Stats: 18STR ; 14DEX ; 16CON ; 8INT ; 6WIS ; 10CAR. Ataca con sus garras afiladas, haciendo 2d12 de daño + sangrado a partir de "AC_enemigo + 2".</t>
-  </si>
-  <si>
     <t>FabianG</t>
   </si>
   <si>
@@ -279,6 +276,27 @@
   </si>
   <si>
     <t>Sira Strand</t>
+  </si>
+  <si>
+    <t>Phoebe Nix</t>
+  </si>
+  <si>
+    <t>Latte Ectrie</t>
+  </si>
+  <si>
+    <t>Duke</t>
+  </si>
+  <si>
+    <t>Panda Rojo. Stats: 9STR ; 15DEX ; 18CON ; 12INT ; 8WIS ; 9CAR. Defiende al usuario y a sus aliados en base al ataque que el enemigo realice. En caso que sea un ataque fisico, formara una burbuja que absorba parte del dano. Si es un ataque magico generara un ligero campo que se deshara de los ataques magicos mas debiles y debilitara los mas fuertes. Los efectos de los ataques no seran ni absorbidos ni reflejaods de ninguna manera por las barreras anteriormente mencionadas.</t>
+  </si>
+  <si>
+    <t>OsoBuho. Stats: 18STR ; 14DEX ; 16CON ; 8INT ; 6WIS ; 10CAR. Ataca con sus garras afiladas, haciendo 2d12 de daño + sangrado a partir de "AC_enemigo + 2". Cualquier daño que reciba ella o su usuaria agregara + 1D4 a sus ataques.</t>
+  </si>
+  <si>
+    <t>Truman</t>
+  </si>
+  <si>
+    <t>Hace un campo gigante de 25 metros a su alrededor (en forma de cubo de 15625 metros^3 con el centro en el usuario) en el cual se curara cualquier ser conciderado aliado mientras dure este efecto. Cada cura es 1D6.</t>
   </si>
 </sst>
 </file>
@@ -768,7 +786,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
@@ -789,10 +807,10 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="M2" s="1">
         <v>5</v>
@@ -848,7 +866,7 @@
         <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>26</v>
@@ -869,10 +887,10 @@
         <v>1</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="M3" s="1">
         <v>14</v>
@@ -997,7 +1015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" ht="57">
       <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
@@ -1007,6 +1025,9 @@
       <c r="C5" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
@@ -1024,6 +1045,12 @@
       </c>
       <c r="J5" s="1">
         <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="M5" s="1">
         <v>10</v>
@@ -1079,7 +1106,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
@@ -1091,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>44</v>
@@ -1100,10 +1127,10 @@
         <v>1</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M6" s="1">
         <v>11</v>
@@ -1159,7 +1186,7 @@
         <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -1180,10 +1207,10 @@
         <v>1</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M7" s="1">
         <v>9</v>
@@ -1228,9 +1255,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" ht="128.25">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
@@ -1238,6 +1265,9 @@
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="E8" s="1" t="s">
         <v>39</v>
       </c>
@@ -1255,6 +1285,12 @@
       </c>
       <c r="J8" s="1">
         <v>1</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="M8" s="1">
         <v>14</v>
@@ -1299,7 +1335,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="42.75">
+    <row r="9" spans="1:24" ht="71.25">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -1310,7 +1346,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -1334,7 +1370,7 @@
         <v>51</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="M9" s="1">
         <v>10</v>
@@ -1381,16 +1417,16 @@
     </row>
     <row r="10" spans="1:24" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>26</v>
@@ -1405,16 +1441,16 @@
         <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="M10" s="1">
         <v>9</v>
@@ -1461,13 +1497,13 @@
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>39</v>
@@ -1479,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
@@ -1532,13 +1568,13 @@
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>39</v>
@@ -1550,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>47</v>
@@ -1603,7 +1639,7 @@
     </row>
     <row r="13" spans="1:24" ht="57">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1">
         <v>9</v>
@@ -1612,10 +1648,10 @@
         <v>2</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1624,15 +1660,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006FE3DCCD7373024E84EE2E195A0A7460" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="9c5fe5080737f498835bd2d9d4e78e12">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7c5d65ae-dd4c-42e9-a760-1483bb566e2c" xmlns:ns4="ecb6ce5d-d8b9-4a2b-93be-18f353c43254" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a74015842085a18a3a3b1f516f0630d7" ns3:_="" ns4:_="">
     <xsd:import namespace="7c5d65ae-dd4c-42e9-a760-1483bb566e2c"/>
@@ -1859,6 +1886,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1868,14 +1904,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE75FF8-4343-4CB1-8F7E-27C6332DD2BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1890,6 +1918,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Uligarm_imports.xlsx
+++ b/Uligarm_imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\UligarmPage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC4DCD8-170F-45B2-B6D2-21E2EE79F887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2BA415-A384-4388-976D-81FD096018BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D9E622A8-95F9-42AD-B0D8-E844E2101417}"/>
   </bookViews>
@@ -242,9 +242,6 @@
     <t>Raychin Gueña</t>
   </si>
   <si>
-    <t>Suena el Punch</t>
-  </si>
-  <si>
     <t>El usuario acumula todo el daño inflingido, recibido y curado en el turno, para liberarlo en un golpe devastador en su siguiente ataque. Este golpe equivale a 1D12 + acumulado. En caso que no pueda acumular nada, el objetivo obtendra un estado negativo elegido por el usuario: Stun (20 segundos / 1 turno), Sangrado (30 segundos / 2 turnos) o Confusion (40 segundos / 3 Turnos)</t>
   </si>
   <si>
@@ -297,6 +294,9 @@
   </si>
   <si>
     <t>Hace un campo gigante de 25 metros a su alrededor (en forma de cubo de 15625 metros^3 con el centro en el usuario) en el cual se curara cualquier ser conciderado aliado mientras dure este efecto. Cada cura es 1D6.</t>
+  </si>
+  <si>
+    <t>Dopamina</t>
   </si>
 </sst>
 </file>
@@ -887,10 +887,10 @@
         <v>1</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="M3" s="1">
         <v>14</v>
@@ -1026,7 +1026,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
@@ -1047,10 +1047,10 @@
         <v>1</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="M5" s="1">
         <v>10</v>
@@ -1106,7 +1106,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>44</v>
@@ -1127,10 +1127,10 @@
         <v>1</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M6" s="1">
         <v>11</v>
@@ -1186,7 +1186,7 @@
         <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -1207,10 +1207,10 @@
         <v>1</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M7" s="1">
         <v>9</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8" spans="1:24" ht="128.25">
       <c r="A8" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
@@ -1266,7 +1266,7 @@
         <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>39</v>
@@ -1287,10 +1287,10 @@
         <v>1</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="M8" s="1">
         <v>14</v>
@@ -1346,7 +1346,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -1370,7 +1370,7 @@
         <v>51</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M9" s="1">
         <v>10</v>
@@ -1651,7 +1651,7 @@
         <v>63</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1660,6 +1660,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006FE3DCCD7373024E84EE2E195A0A7460" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="9c5fe5080737f498835bd2d9d4e78e12">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7c5d65ae-dd4c-42e9-a760-1483bb566e2c" xmlns:ns4="ecb6ce5d-d8b9-4a2b-93be-18f353c43254" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a74015842085a18a3a3b1f516f0630d7" ns3:_="" ns4:_="">
     <xsd:import namespace="7c5d65ae-dd4c-42e9-a760-1483bb566e2c"/>
@@ -1886,15 +1895,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1904,6 +1904,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE75FF8-4343-4CB1-8F7E-27C6332DD2BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1918,14 +1926,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F26B1A-F46F-4EEC-8194-E2F786EFBD55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
